--- a/tables/Opioid_Tier1_HedgesG.xlsx
+++ b/tables/Opioid_Tier1_HedgesG.xlsx
@@ -502,9 +502,7 @@
       <c r="B2" t="n">
         <v>2000</v>
       </c>
-      <c r="C2" t="n">
-        <v>27</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Ibogaine</t>
@@ -512,11 +510,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>9.59</v>
+          <t>F (multi-df, within-subjects repeated-measures ANOVA)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>F(3,24) = 81.38</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ibogaine</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -598,14 +598,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Krupitsky 2007</t>
+          <t>Krupitsky 2002</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50 vs 22.2</t>
+          <t>50 vs 60</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
+          <t>Two-group proportions from figure (approximate); downgrade to Tier 2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -643,14 +643,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Krupitsky 2002</t>
+          <t>Krupitsky 2007</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="C5" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25 vs 3</t>
+          <t>50 vs 22.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Two-group proportions from figure (approximate); downgrade to Tier 2</t>
+          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -704,13 +704,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Group means (Tx vs Ctrl)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>22.5 vs 13.9</t>
-        </is>
+          <t>Exposure-response linear mixed-effects regression slope (change from baseline, placebo-corrected QTcI vs. plasma noribogaine concentration)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.17</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -749,7 +747,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -783,7 +781,7 @@
         <v>1973</v>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -814,22 +812,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.4691813788280079</v>
+        <v>0.4725621789955972</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4642770438576803</v>
+        <v>0.4675526859320396</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05551049441522451</v>
+        <v>0.05629181858987852</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2356066518908677</v>
+        <v>0.2372589694613852</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00248800615157968</v>
+        <v>0.002525105787724635</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9260660815637809</v>
+        <v>0.9325802660763547</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Opioid_Tier1_HedgesG.xlsx
+++ b/tables/Opioid_Tier1_HedgesG.xlsx
@@ -502,7 +502,9 @@
       <c r="B2" t="n">
         <v>2000</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Ibogaine</t>
@@ -561,39 +563,23 @@
       <c r="F3" t="n">
         <v>1.39</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d pre-computed from group means (96.6 vs 79.4 mmHg MAP) and SDs (13.8, 10.8); equal groups assumed; direction favors treatment (lower MAP)</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.368167539267016</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0987188241550396</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.3141955189926164</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.7523443220414874</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.983990756492544</v>
-      </c>
+          <t>Excluded from Tier 1: the only convertible statistic (d=1.39 from peak MAP, 96.6 vs 79.4 mmHg) measures blood pressure, not substance use. output.md rules the OOWS-A withdrawal-severity score the primary outcome, and it is reported only as 'p&lt;0.05' with no test statistic, so no SUD-outcome effect size can be derived without computing a test the authors did not report.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/tables/Opioid_Tier1_HedgesG.xlsx
+++ b/tables/Opioid_Tier1_HedgesG.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,102 +717,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P.L. Prior 2014</t>
+          <t>Savage 1973</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2014</v>
+        <v>1973</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ibogaine</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
+          <t>Chi-squared</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>3.86</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>chi2</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>approx</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>F(3,12) has 3-df numerator; not reducible to 1-df between-groups comparison</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Savage 1973</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1973</v>
-      </c>
-      <c r="C8" t="n">
-        <v>73</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LSD</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chi-squared</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>chi2</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>approx</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
           <t>χ²=3.86, df=1; 9/36 vs 2/37 abstinent at 12mo</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J7" t="n">
         <v>0.4725621789955972</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K7" t="n">
         <v>0.4675526859320396</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L7" t="n">
         <v>0.05629181858987852</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M7" t="n">
         <v>0.2372589694613852</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N7" t="n">
         <v>0.002525105787724635</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O7" t="n">
         <v>0.9325802660763547</v>
       </c>
     </row>

--- a/tables/Opioid_Tier1_HedgesG.xlsx
+++ b/tables/Opioid_Tier1_HedgesG.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Excluded from Tier 1: the only convertible statistic (d=1.39 from peak MAP, 96.6 vs 79.4 mmHg) measures blood pressure, not substance use. output.md rules the OOWS-A withdrawal-severity score the primary outcome, and it is reported only as 'p&lt;0.05' with no test statistic, so no SUD-outcome effect size can be derived without computing a test the authors did not report.</t>
+          <t>Excluded from Tier 1: the only convertible statistic (d=1.39 from peak MAP, 96.6 vs 79.4 mmHg) measures blood pressure, not substance use. clinical_adjudication.md rules the OOWS-A withdrawal-severity score the primary outcome, and it is reported only as 'p&lt;0.05' with no test statistic, so no SUD-outcome effect size can be derived without computing a test the authors did not report.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
